--- a/GrocceryApplication/src/test/resources/TestData.xlsx
+++ b/GrocceryApplication/src/test/resources/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeffy P Jerry\eclipse-workspace\GrocceryApplication\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeffy P Jerry\git\Project\GrocceryApplication\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE6D4B4-0A36-4974-930C-BB619463C183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92D4291-E268-45A8-AA02-6B83A7C276E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GrocceryApplication/src/test/resources/TestData.xlsx
+++ b/GrocceryApplication/src/test/resources/TestData.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeffy P Jerry\git\Project\GrocceryApplication\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92D4291-E268-45A8-AA02-6B83A7C276E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CB8D76-867C-4167-9C28-81416779C944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
+    <sheet name="Adminpage" sheetId="2" r:id="rId2"/>
+    <sheet name="NewsPage" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,12 +27,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="4">
   <si>
     <t>admin</t>
   </si>
   <si>
     <t>admins</t>
+  </si>
+  <si>
+    <t>jeffy</t>
+  </si>
+  <si>
+    <t>New Product launched…...</t>
   </si>
 </sst>
 </file>
@@ -348,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -383,6 +391,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39255CA-0109-46C1-BEDC-ADA91A645352}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91779ACE-2B65-4008-81AF-B4AEC49BB007}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
